--- a/artfynd/A 39048-2024 artfynd.xlsx
+++ b/artfynd/A 39048-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120838396</v>
+        <v>120833458</v>
       </c>
       <c r="B2" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -716,14 +716,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Man-Pålmyran, Man-Pålmyran, Ång</t>
+          <t>Bråddödfallet, Bråddödfallet, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629458</v>
+        <v>629437</v>
       </c>
       <c r="R2" t="n">
-        <v>6972752</v>
+        <v>6972622</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120838222</v>
+        <v>120833289</v>
       </c>
       <c r="B3" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,14 +818,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Manhöjden, Manhöjden, Ång</t>
+          <t>Man-Pålmyran, Man-Pålmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629509</v>
+        <v>629370</v>
       </c>
       <c r="R3" t="n">
-        <v>6972787</v>
+        <v>6972665</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120833289</v>
+        <v>120838396</v>
       </c>
       <c r="B4" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,34 +900,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Man-Pålmyran, Man-Pålmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629370</v>
+        <v>629458</v>
       </c>
       <c r="R4" t="n">
-        <v>6972665</v>
+        <v>6972752</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120833522</v>
+        <v>120838222</v>
       </c>
       <c r="B5" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,14 +1027,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bråddödfallet, Bråddödfallet, Ång</t>
+          <t>Manhöjden, Manhöjden, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629458</v>
+        <v>629509</v>
       </c>
       <c r="R5" t="n">
-        <v>6972613</v>
+        <v>6972787</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120833458</v>
+        <v>120833522</v>
       </c>
       <c r="B6" t="n">
-        <v>57348</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,39 +1109,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bråddödfallet, Bråddödfallet, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629437</v>
+        <v>629458</v>
       </c>
       <c r="R6" t="n">
-        <v>6972622</v>
+        <v>6972613</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1198,7 +1198,7 @@
         <v>121209738</v>
       </c>
       <c r="B7" t="n">
-        <v>79708</v>
+        <v>79711</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>121209731</v>
       </c>
       <c r="B8" t="n">
-        <v>79639</v>
+        <v>79642</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121208670</v>
+        <v>121208373</v>
       </c>
       <c r="B9" t="n">
-        <v>90687</v>
+        <v>79682</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>629622</v>
+        <v>629632</v>
       </c>
       <c r="R9" t="n">
-        <v>6972760</v>
+        <v>6972764</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1504,7 +1504,7 @@
         <v>121208540</v>
       </c>
       <c r="B10" t="n">
-        <v>94474</v>
+        <v>94484</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121208373</v>
+        <v>121208670</v>
       </c>
       <c r="B11" t="n">
-        <v>79679</v>
+        <v>90697</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629632</v>
+        <v>629622</v>
       </c>
       <c r="R11" t="n">
-        <v>6972764</v>
+        <v>6972760</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1708,7 +1708,7 @@
         <v>121209747</v>
       </c>
       <c r="B12" t="n">
-        <v>79680</v>
+        <v>79683</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 39048-2024 artfynd.xlsx
+++ b/artfynd/A 39048-2024 artfynd.xlsx
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121209738</v>
+        <v>121208670</v>
       </c>
       <c r="B7" t="n">
-        <v>79711</v>
+        <v>90697</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,38 +1207,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bråddödfallet, Bråddödfallet, Ång</t>
+          <t>Manhöjden, Manhöjden, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629494</v>
+        <v>629622</v>
       </c>
       <c r="R7" t="n">
-        <v>6972667</v>
+        <v>6972760</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121209731</v>
+        <v>121209738</v>
       </c>
       <c r="B8" t="n">
-        <v>79642</v>
+        <v>79711</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121208373</v>
+        <v>121208540</v>
       </c>
       <c r="B9" t="n">
-        <v>79682</v>
+        <v>94484</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>629632</v>
+        <v>629622</v>
       </c>
       <c r="R9" t="n">
-        <v>6972764</v>
+        <v>6972760</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121208540</v>
+        <v>121208373</v>
       </c>
       <c r="B10" t="n">
-        <v>94484</v>
+        <v>79682</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629622</v>
+        <v>629632</v>
       </c>
       <c r="R10" t="n">
-        <v>6972760</v>
+        <v>6972764</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121208670</v>
+        <v>121209731</v>
       </c>
       <c r="B11" t="n">
-        <v>90697</v>
+        <v>79642</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,38 +1615,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Manhöjden, Manhöjden, Ång</t>
+          <t>Bråddödfallet, Bråddödfallet, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629622</v>
+        <v>629494</v>
       </c>
       <c r="R11" t="n">
-        <v>6972760</v>
+        <v>6972667</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>

--- a/artfynd/A 39048-2024 artfynd.xlsx
+++ b/artfynd/A 39048-2024 artfynd.xlsx
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121208670</v>
+        <v>121208540</v>
       </c>
       <c r="B7" t="n">
-        <v>90697</v>
+        <v>94496</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121209738</v>
+        <v>121208670</v>
       </c>
       <c r="B8" t="n">
-        <v>79711</v>
+        <v>90709</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,38 +1309,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bråddödfallet, Bråddödfallet, Ång</t>
+          <t>Manhöjden, Manhöjden, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>629494</v>
+        <v>629622</v>
       </c>
       <c r="R8" t="n">
-        <v>6972667</v>
+        <v>6972760</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121208540</v>
+        <v>121208373</v>
       </c>
       <c r="B9" t="n">
-        <v>94484</v>
+        <v>79685</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>629622</v>
+        <v>629632</v>
       </c>
       <c r="R9" t="n">
-        <v>6972760</v>
+        <v>6972764</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121208373</v>
+        <v>121209731</v>
       </c>
       <c r="B10" t="n">
-        <v>79682</v>
+        <v>79645</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,38 +1513,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Manhöjden, Manhöjden, Ång</t>
+          <t>Bråddödfallet, Bråddödfallet, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629632</v>
+        <v>629494</v>
       </c>
       <c r="R10" t="n">
-        <v>6972764</v>
+        <v>6972667</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121209731</v>
+        <v>121209738</v>
       </c>
       <c r="B11" t="n">
-        <v>79642</v>
+        <v>79714</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1708,7 +1708,7 @@
         <v>121209747</v>
       </c>
       <c r="B12" t="n">
-        <v>79683</v>
+        <v>79686</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 39048-2024 artfynd.xlsx
+++ b/artfynd/A 39048-2024 artfynd.xlsx
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121208540</v>
+        <v>121208670</v>
       </c>
       <c r="B7" t="n">
-        <v>94496</v>
+        <v>90710</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121208670</v>
+        <v>121208540</v>
       </c>
       <c r="B8" t="n">
-        <v>90709</v>
+        <v>94497</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121208373</v>
+        <v>121209738</v>
       </c>
       <c r="B9" t="n">
-        <v>79685</v>
+        <v>79714</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,38 +1411,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Manhöjden, Manhöjden, Ång</t>
+          <t>Bråddödfallet, Bråddödfallet, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>629632</v>
+        <v>629494</v>
       </c>
       <c r="R9" t="n">
-        <v>6972764</v>
+        <v>6972667</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121209731</v>
+        <v>121208373</v>
       </c>
       <c r="B10" t="n">
-        <v>79645</v>
+        <v>79685</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,38 +1513,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bråddödfallet, Bråddödfallet, Ång</t>
+          <t>Manhöjden, Manhöjden, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629494</v>
+        <v>629632</v>
       </c>
       <c r="R10" t="n">
-        <v>6972667</v>
+        <v>6972764</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121209738</v>
+        <v>121209731</v>
       </c>
       <c r="B11" t="n">
-        <v>79714</v>
+        <v>79645</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>

--- a/artfynd/A 39048-2024 artfynd.xlsx
+++ b/artfynd/A 39048-2024 artfynd.xlsx
@@ -1198,7 +1198,7 @@
         <v>121208670</v>
       </c>
       <c r="B7" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121208540</v>
+        <v>121209731</v>
       </c>
       <c r="B8" t="n">
-        <v>94497</v>
+        <v>79648</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,34 +1313,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2809</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Manhöjden, Manhöjden, Ång</t>
+          <t>Bråddödfallet, Bråddödfallet, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>629622</v>
+        <v>629494</v>
       </c>
       <c r="R8" t="n">
-        <v>6972760</v>
+        <v>6972667</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1402,7 +1402,7 @@
         <v>121209738</v>
       </c>
       <c r="B9" t="n">
-        <v>79714</v>
+        <v>79717</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121208373</v>
+        <v>121208540</v>
       </c>
       <c r="B10" t="n">
-        <v>79685</v>
+        <v>94500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629632</v>
+        <v>629622</v>
       </c>
       <c r="R10" t="n">
-        <v>6972764</v>
+        <v>6972760</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121209731</v>
+        <v>121208373</v>
       </c>
       <c r="B11" t="n">
-        <v>79645</v>
+        <v>79688</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,38 +1615,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bråddödfallet, Bråddödfallet, Ång</t>
+          <t>Manhöjden, Manhöjden, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629494</v>
+        <v>629632</v>
       </c>
       <c r="R11" t="n">
-        <v>6972667</v>
+        <v>6972764</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1708,7 +1708,7 @@
         <v>121209747</v>
       </c>
       <c r="B12" t="n">
-        <v>79686</v>
+        <v>79689</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 39048-2024 artfynd.xlsx
+++ b/artfynd/A 39048-2024 artfynd.xlsx
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121209731</v>
+        <v>121208540</v>
       </c>
       <c r="B8" t="n">
-        <v>79648</v>
+        <v>94500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,34 +1313,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>2809</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bråddödfallet, Bråddödfallet, Ång</t>
+          <t>Manhöjden, Manhöjden, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>629494</v>
+        <v>629622</v>
       </c>
       <c r="R8" t="n">
-        <v>6972667</v>
+        <v>6972760</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121209738</v>
+        <v>121208373</v>
       </c>
       <c r="B9" t="n">
-        <v>79717</v>
+        <v>79688</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,38 +1411,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bråddödfallet, Bråddödfallet, Ång</t>
+          <t>Manhöjden, Manhöjden, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>629494</v>
+        <v>629632</v>
       </c>
       <c r="R9" t="n">
-        <v>6972667</v>
+        <v>6972764</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121208540</v>
+        <v>121209738</v>
       </c>
       <c r="B10" t="n">
-        <v>94500</v>
+        <v>79717</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,34 +1517,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2809</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Manhöjden, Manhöjden, Ång</t>
+          <t>Bråddödfallet, Bråddödfallet, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629622</v>
+        <v>629494</v>
       </c>
       <c r="R10" t="n">
-        <v>6972760</v>
+        <v>6972667</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121208373</v>
+        <v>121209731</v>
       </c>
       <c r="B11" t="n">
-        <v>79688</v>
+        <v>79648</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,38 +1615,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Manhöjden, Manhöjden, Ång</t>
+          <t>Bråddödfallet, Bråddödfallet, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629632</v>
+        <v>629494</v>
       </c>
       <c r="R11" t="n">
-        <v>6972764</v>
+        <v>6972667</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>

--- a/artfynd/A 39048-2024 artfynd.xlsx
+++ b/artfynd/A 39048-2024 artfynd.xlsx
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121208670</v>
+        <v>121208373</v>
       </c>
       <c r="B7" t="n">
-        <v>90713</v>
+        <v>79689</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629622</v>
+        <v>629632</v>
       </c>
       <c r="R7" t="n">
-        <v>6972760</v>
+        <v>6972764</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121208540</v>
+        <v>121209731</v>
       </c>
       <c r="B8" t="n">
-        <v>94500</v>
+        <v>79649</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,34 +1313,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2809</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Manhöjden, Manhöjden, Ång</t>
+          <t>Bråddödfallet, Bråddödfallet, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>629622</v>
+        <v>629494</v>
       </c>
       <c r="R8" t="n">
-        <v>6972760</v>
+        <v>6972667</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121208373</v>
+        <v>121208540</v>
       </c>
       <c r="B9" t="n">
-        <v>79688</v>
+        <v>94506</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>629632</v>
+        <v>629622</v>
       </c>
       <c r="R9" t="n">
-        <v>6972764</v>
+        <v>6972760</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121209738</v>
+        <v>121208670</v>
       </c>
       <c r="B10" t="n">
-        <v>79717</v>
+        <v>90719</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,38 +1513,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bråddödfallet, Bråddödfallet, Ång</t>
+          <t>Manhöjden, Manhöjden, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629494</v>
+        <v>629622</v>
       </c>
       <c r="R10" t="n">
-        <v>6972667</v>
+        <v>6972760</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121209731</v>
+        <v>121209738</v>
       </c>
       <c r="B11" t="n">
-        <v>79648</v>
+        <v>79718</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1708,7 +1708,7 @@
         <v>121209747</v>
       </c>
       <c r="B12" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 39048-2024 artfynd.xlsx
+++ b/artfynd/A 39048-2024 artfynd.xlsx
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121208373</v>
+        <v>121208540</v>
       </c>
       <c r="B7" t="n">
-        <v>79689</v>
+        <v>94507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629632</v>
+        <v>629622</v>
       </c>
       <c r="R7" t="n">
-        <v>6972764</v>
+        <v>6972760</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121209731</v>
+        <v>121208670</v>
       </c>
       <c r="B8" t="n">
-        <v>79649</v>
+        <v>90720</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,38 +1309,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bråddödfallet, Bråddödfallet, Ång</t>
+          <t>Manhöjden, Manhöjden, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>629494</v>
+        <v>629622</v>
       </c>
       <c r="R8" t="n">
-        <v>6972667</v>
+        <v>6972760</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121208540</v>
+        <v>121208373</v>
       </c>
       <c r="B9" t="n">
-        <v>94506</v>
+        <v>79690</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>629622</v>
+        <v>629632</v>
       </c>
       <c r="R9" t="n">
-        <v>6972760</v>
+        <v>6972764</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121208670</v>
+        <v>121209731</v>
       </c>
       <c r="B10" t="n">
-        <v>90719</v>
+        <v>79650</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,38 +1513,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Manhöjden, Manhöjden, Ång</t>
+          <t>Bråddödfallet, Bråddödfallet, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629622</v>
+        <v>629494</v>
       </c>
       <c r="R10" t="n">
-        <v>6972760</v>
+        <v>6972667</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1606,7 +1606,7 @@
         <v>121209738</v>
       </c>
       <c r="B11" t="n">
-        <v>79718</v>
+        <v>79719</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>121209747</v>
       </c>
       <c r="B12" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 39048-2024 artfynd.xlsx
+++ b/artfynd/A 39048-2024 artfynd.xlsx
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121208670</v>
+        <v>121209731</v>
       </c>
       <c r="B8" t="n">
-        <v>90720</v>
+        <v>79650</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,38 +1309,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Manhöjden, Manhöjden, Ång</t>
+          <t>Bråddödfallet, Bråddödfallet, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>629622</v>
+        <v>629494</v>
       </c>
       <c r="R8" t="n">
-        <v>6972760</v>
+        <v>6972667</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121209731</v>
+        <v>121209738</v>
       </c>
       <c r="B10" t="n">
-        <v>79650</v>
+        <v>79719</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121209738</v>
+        <v>121208670</v>
       </c>
       <c r="B11" t="n">
-        <v>79719</v>
+        <v>90720</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,38 +1615,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bråddödfallet, Bråddödfallet, Ång</t>
+          <t>Manhöjden, Manhöjden, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629494</v>
+        <v>629622</v>
       </c>
       <c r="R11" t="n">
-        <v>6972667</v>
+        <v>6972760</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
